--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Payer analysis / payer mix</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+          <t>Payer analysis / payer mix (per-payer rollup: claim count, billed, paid, outstanding, denial rate, collection rate, avg days-to-pay)</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Custom reports (reports landing page + report viewer)</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+          <t>Custom reports (reports landing page + report viewer with filters, column picker, views, export, sort, pagination, aggregates bar, heat-map visualisation) — 35 registered reports</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Denial heat map</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+          <t>Denial heat map (category × month pivot with intensity gradient; count/amount toggle; CARC code classifier)</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,15 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F5132"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,12 @@
         <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1F2D5"/>
+        <bgColor rgb="00D1F2D5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -102,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -124,6 +137,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -513,6 +530,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -678,9 +700,14 @@
           <t>ISO 27001 alignment (policy + evidence + risk register)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — Compliance Ops UI hub (§4s)</t>
         </is>
       </c>
     </row>
@@ -695,9 +722,14 @@
           <t>SOC2 certifiable controls (audit log, access review, incident register)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — Compliance Ops UI hub (§4s)</t>
         </is>
       </c>
     </row>
@@ -1732,9 +1764,14 @@
           <t>Eligibility verification (270/271)</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>⛔ Planned</t>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Shipped 2026-04-23 (§4o) + P0 expansion 2026-04-30 (§4p)</t>
         </is>
       </c>
     </row>
@@ -2157,9 +2194,14 @@
           <t>Access review cycles</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — register in Compliance UI (§4s)</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2864,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -2832,7 +2874,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2842,9 +2884,10 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>9</v>
-      </c>
-    </row>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -1557,12 +1557,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Integrated payment processing (Stripe playbook ready to wire)</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>⛔ Planned</t>
+          <t>Integrated payment processing (Helcim — HelcimPay.js + Customer Vault)</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — HelcimPay.js hosted iframe + Customer Vault saved cards (per-tenant credentials, encrypted)</t>
         </is>
       </c>
     </row>
@@ -1577,9 +1582,14 @@
           <t>Recurring / saved payment methods</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>⛔ Planned</t>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — via Helcim Customer Vault (card_token charge endpoint POST /api/billing/helcim/charges/saved-card)</t>
         </is>
       </c>
     </row>
@@ -1713,9 +1723,14 @@
           <t>Refund / void tracking</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — POST /api/billing/helcim/refunds with full + partial refund support</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2449,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Payment integrations (Stripe playbook)</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>🟡 Partial</t>
+          <t>Payment integrations (per-tenant Helcim credentials with AES-256 encryption, webhook signature verification)</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — replaces the Stripe playbook; Helcim chosen by user</t>
         </is>
       </c>
     </row>
@@ -2454,9 +2474,14 @@
           <t>Helcim</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>⛔ Planned</t>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — settings UI at /settings/payments, HelcimPayDialog modal, refund + saved-card + webhook routes</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2889,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -2874,7 +2899,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -2884,7 +2909,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6"/>

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -141,6 +141,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2839,6 +2840,72 @@
       <c r="C134" s="4" t="inlineStr">
         <is>
           <t>✅ Shipped</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Billing &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Recurring auto-charge engine (payment plans + treatment-plan auto-pay + statement auto-pay)</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — payment_schedules + payment_schedule_runs collections, async background worker (60s interval), retry-with-1d/3d/7d backoff + admin notification on terminal failure, manual run-now + scheduler/tick endpoints, UI in patient ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Billing &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Payment plan UX (split charge into N installments)</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — PaymentPlansCard.jsx with create/pause/resume/cancel/run-now + charge history dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Billing &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Saved cards UI on patient ledger</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-02 — SavedCardsCard.jsx with charge-now + delete; default-card semantics; linked to HelcimPayDialog 'Save card on file' checkbox</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2946,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -2889,7 +2956,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1240,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — Portal 'Check in' CTA on today's appointments + public /kiosk tablet flow (last-name + DOB matcher); flips status→arrived with arrived_via=portal|kiosk.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1262,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — /portal/book request-only flow (1–3 preferred time slots + reason + notes) with /scheduling/booking-requests staff queue; approve materialises a real appointment + fires SMS confirmation.</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1284,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — Chiropractic starter pack (Oswestry / NDI / PSFS / NPRS) delivered to patient via SMS deep-link; code-first templates with built-in scoring; submit writes into outcome_entries so Phase-7 trends pick it up automatically. Empty/missing required answers rejected 422.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1306,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — Backend SMS service (tenant-scoped Twilio creds encrypted AES-256, log-only fallback, signature-verified webhook, inbox threads/messages, /sms/send, /sms/settings); OTP request/verify with 10-min TTL + 5-attempt cap; /settings/sms admin UI. Staff inbox UI still pending (P1 backlog).</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2536,12 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — Per-tenant credentials (Account SID + Auth Token encrypted; Messaging Service SID OR from-number), enable toggle, /sms/settings/test, log-only fallback when not enabled, X-Twilio-Signature HMAC verification on inbound webhook, sms_outbound_log + sms_threads + sms_messages collections.</t>
         </is>
       </c>
     </row>
@@ -2906,6 +2931,72 @@
       <c r="D137" t="inlineStr">
         <is>
           <t>Shipped 2026-05-02 — SavedCardsCard.jsx with charge-now + delete; default-card semantics; linked to HelcimPayDialog 'Save card on file' checkbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Patient Intake &amp; Engagement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kiosk public check-in (tablet at front desk)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — public POST /api/kiosk/check-in (no auth; X-Kiosk-Tenant header); DOB + last-name matcher pulls today's scheduled appointment and flips status→arrived; success screen auto-resets after 10s for next patient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Patient Intake &amp; Engagement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Patient-portal booking-request queue (staff side)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — /scheduling/booking-requests with status filter chips; Approve dialog supports overriding start_time + duration + optional note; Decline with reason; both fire audit rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Security &amp; Identity (CCMS-specific)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Patient portal phone-first SMS OTP login</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-16 (§5a) — POST /api/portal/auth/otp/{request,verify}; 6-digit code hashed SHA-256 with 10-min TTL + 5-attempt cap; never reveals whether phone is registered; auto-provisions users{role=patient, linked_patient_id, portal_otp_only=true} on first successful verify. /portal/login UI surfaces dev_code toast when Twilio is in log-only mode.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +3070,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2558,7 +2558,12 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-17 — Per-tenant Resend credentials encrypted AES-256 (mirrors Twilio pattern), enable toggle, /settings/email admin UI, test-send card, log-only fallback, email_outbound_log; notifications/email.py prefers tenant creds first then env-var fallback. Outbound log audit-trail.</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2614,12 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>⛔ Planned</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-17 — Emergent-managed Google sign-in for STAFF only (admin/doctor/staff); patients stay on SMS OTP. Per-tenant enable toggle + email-domain allowlist + default_role at /settings/google. POST /api/auth/google/exchange validates Emergent session_token, mints our JWT cookies, audit row on every sign-in (success and failure). 'Sign in with Google' button on /login appears only when /api/auth/google/availability=true.</t>
         </is>
       </c>
     </row>
@@ -2997,6 +3007,50 @@
       <c r="D140" t="inlineStr">
         <is>
           <t>Shipped 2026-02-16 (§5a) — POST /api/portal/auth/otp/{request,verify}; 6-digit code hashed SHA-256 with 10-min TTL + 5-attempt cap; never reveals whether phone is registered; auto-provisions users{role=patient, linked_patient_id, portal_otp_only=true} on first successful verify. /portal/login UI surfaces dev_code toast when Twilio is in log-only mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Patient Intake &amp; Engagement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Two-way SMS staff inbox UI</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-17 — /communications/sms thread list + message panel + reply box; clears unread counter on open; mobile-responsive (single-pane on small screens). Backed by sms_threads + sms_messages collections (already shipped backend-side in §5a).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Security &amp; Identity (CCMS-specific)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Per-tenant Google OAuth domain allowlist</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Shipped 2026-02-17 — Tenant admins manage allow-listed email domains at /settings/google. New users from allow-listed domains auto-provision as the configured default_role on first Google sign-in; everyone else gets a 403 with clear messaging. Existing users (matched by email) sign in regardless of domain. Audit rows on every accept and reject.</t>
         </is>
       </c>
     </row>

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -815,7 +815,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>⛔ Planned</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5 via Emergent LLM Key. Surfaces: chart-prep brief on patient chart + AI assist rail (prior-sections, since-last-diff, draft-sections) in follow-up note editor. Smart cache keyed on content hash. Audit ai_usage rows are PHI-safe. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3106,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -3121,7 +3126,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3056,6 +3056,28 @@
       <c r="D142" t="inlineStr">
         <is>
           <t>Shipped 2026-02-17 — Tenant admins manage allow-listed email domains at /settings/google. New users from allow-listed domains auto-provision as the configured default_role on first Google sign-in; everyone else gets a 403 with clear messaging. Existing users (matched by email) sign in regardless of domain. Audit rows on every accept and reject.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Patient-facing AI visit brief (portal preview)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Plain-language pre-visit summary in patient portal. Claude Sonnet 4.5 via Emergent LLM Key. Separate cache surface (patient_visit_brief) and prompt that strips ICD codes / med names / jargon. Endpoints: GET/POST /api/portal/visit-brief. Component: portal/PortalVisitBriefCard.jsx. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3118,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
@@ -3106,7 +3128,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4">
@@ -3158,7 +3180,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -781,7 +781,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>⛔ Planned</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 4.5 strict-JSON SOAP draft from transcript + optional addendum. Doctor-only side panel in Follow-Up Note + Initial Exam editors with per-section Apply + Apply-all. Endpoint POST /api/scribe/encounters/{note_type}/{note_id}/soap/draft. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -798,7 +803,12 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>⛔ Planned</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OpenAI Whisper (whisper-1) via Emergent LLM Key + emergentintegrations. In-browser MediaRecorder, click-to-start/stop, no hard cap, ≤25MB chunks. Audio held in encrypted Emergent object storage, soft-deleted on note sign. Endpoints: POST /api/scribe/audio, GET/DELETE chunks. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3138,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
@@ -3148,7 +3158,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3088,6 +3088,72 @@
       <c r="D143" t="inlineStr">
         <is>
           <t>Plain-language pre-visit summary in patient portal. Claude Sonnet 4.5 via Emergent LLM Key. Separate cache surface (patient_visit_brief) and prompt that strips ICD codes / med names / jargon. Endpoints: GET/POST /api/portal/visit-brief. Component: portal/PortalVisitBriefCard.jsx. Shipped 2026-05-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Inline CPT/ICD coding suggestions (closes documentation→billing loop)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Auto-fires from Apply-All in ScribePanel. POST /api/scribe/encounters/{note_type}/{note_id}/coding-suggest. Doctor-only. Returns CPT codes (with modifier hints), ICD-10 codes (with primary candidate flag), and documentation warnings. Shipped 2026-05-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Natural-language semantic search across patient charts</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>POST /api/ai/search. Asks Claude Sonnet 4.5 to rank up to 30 chart snippets (signed follow-ups, exams, dx, plans, outcomes) against a free-text query. Returns 2-3 sentence answer with [s#] citations + ranked snippet cards. Cached per (patient_id, query_hash). Shipped 2026-05-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SOAP-template overrides per location/provider</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>GET/PUT/DELETE /api/ai/templates. Admin-only page at /settings/ai-templates. Tenant → location → provider override stack appended to the system prompt at runtime. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3194,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
@@ -3138,7 +3204,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4">
@@ -3190,7 +3256,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3154,6 +3154,28 @@
       <c r="D146" t="inlineStr">
         <is>
           <t>GET/PUT/DELETE /api/ai/templates. Admin-only page at /settings/ai-templates. Tenant → location → provider override stack appended to the system prompt at runtime. Shipped 2026-05-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Natural-language scheduling (Quick-book)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Plain-English appointment booking. Claude Sonnet 4.5 resolves patient/provider/type/location/start from free text, with hallucination-guarded ID validation. Two-phase parse → confirm UI. Endpoints: POST /api/scheduling/nl/parse, /api/scheduling/nl/create. Shipped 2026-05-04.</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3216,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -3204,7 +3226,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
@@ -3256,7 +3278,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">

--- a/memory/CCMS_Features.xlsx
+++ b/memory/CCMS_Features.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -142,6 +142,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -881,7 +882,12 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>⛔ Planned</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 (see row 147 — Natural-language scheduling Quick-book covers create + reschedule + cancel intents). Endpoints: POST /api/scheduling/nl/parse, /nl/create, /nl/reschedule, /nl/cancel. Frontend: scheduling/NLBookCard.jsx with intent-aware UI (patient/provider hidden on reschedule/cancel).</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2479,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>🟡 Partial</t>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — Change Healthcare sandbox adapter wired end-to-end. ChangeHealthcareAdapter (sandbox/disabled/production modes), OptumAdapter, NoneAdapter. Per-payer routing via clearinghouse_route. Sandbox returns synthetic external IDs (chc-sbx-{hex}) without putting PHI on the wire. Production-mode live HTTPS transport scaffolded but pending real-credential phase. Adapter selection in services/billing/clearinghouse/routing.py.</t>
         </is>
       </c>
     </row>
@@ -3176,6 +3187,248 @@
       <c r="D147" t="inlineStr">
         <is>
           <t>Plain-English appointment booking. Claude Sonnet 4.5 resolves patient/provider/type/location/start from free text, with hallucination-guarded ID validation. Two-phase parse → confirm UI. Endpoints: POST /api/scheduling/nl/parse, /api/scheduling/nl/create. Shipped 2026-05-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Send to claim from AI Scribe SOAP draft (one-click)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — POST /api/scribe/encounters/{note_type}/{note_id}/send-to-claim creates a draft claim with all accepted CPT/ICD lines from the scribe. Auto-resolves billed_cents via the payer fee schedule when the caller passes 0. Returns price_sources[] for transparency. Frontend: ScribePanel.jsx 'Create draft claim' button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Natural-language scheduling — reschedule and cancel intents</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — Quick-book parser now resolves intent ∈ {create, reschedule, cancel} and target_appointment_id from free text. POST /api/scheduling/nl/reschedule, /nl/cancel. Conflict (409) surfaces inline. NLBookCard.jsx hides irrelevant inputs based on intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Server-side semantic search across providers (paginated picker)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — GET /api/auth/users now supports q/limit/offset (regex-escaped, case-insensitive across name/email). AITemplatesPage.jsx debounces 250 ms and re-fetches from the server, caps at 200 results per request. Scales to tenants with hundreds of providers without shipping the full list to the browser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Billing &amp; RCM</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>One-click Submit-to-Clearinghouse (quick-submit)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — POST /api/billing/claims/{claim_id}/quick-submit runs scrubber → ready-transition → adapter.submit in a single transactional call. Sandbox/disabled adapters allow scrubber failures (submitted_with_warnings flag) so demos and pre-enrollment testing keep working without sending PHI on the wire; production strictly enforces scrubber pass. UI: claim-quick-submit-btn on /billing/claims/{id} AND scribe-quick-submit-btn on the AI Scribe panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Billing &amp; RCM</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Live submission timeline (WebSocket + polling)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — WS /api/billing/ws/claims/{claim_id}/events streams claim_events to ClaimDetail in real-time. Cookie-authenticated, tenant + claim ownership validated, 25-s heartbeat. Fan-out via in-process pub/sub (services/billing/timeline_pubsub.py). Frontend ClaimTimeline.jsx connects to WS, falls back to 30-s polling, dedupes by event id. Live/Connecting/Polling pill, latest-event card, full history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Billing &amp; RCM</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sandbox ack simulator (synthetic 999/277CA/outcome/ERA chain)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — services/billing/sandbox_ack_simulator.py schedules a fire-and-forget asyncio walker on every sandbox _do_submit_claim. Emits ack_999_accepted (+5 s) → ack_277ca_accepted (+10 s) → outcome_recorded (+15 s) → era_posted (+20 s); flips claim status to paid. Drives the live timeline so the demo animates without real network traffic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Billing &amp; RCM</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Production-mode ack poller (999/277CA fetch loop)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 (scaffold) — services/billing/ack_poller.py runs as a startup background task. Every 60 s queries production-mode submissions and asks the resolved adapter for 999/277CA acks. Adapters return None today so the poller is a quiet no-op; live transport plug-in ready for the real-creds phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Billing &amp; RCM</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Fee-schedule auto-resolution on send-to-claim</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — services/scribe/router.py::send_to_claim now calls resolve_charge_price() for every CPT line where caller passes billed_cents=0. Resolution order: payer schedule → self_pay schedule → catalog → 0. Response exposes price_sources[] per line so the doctor can see where each price came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Change Healthcare sandbox adapter (live UI flow)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — Sandbox mode (CLEARINGHOUSE_CHC_MODE=sandbox) returns synthetic external IDs (chc-sbx-{hex}) without HTTPS calls; production mode scaffolded but logs a WARNING and behaves as sandbox until live transport is enabled. Wired end-to-end through one-click Submit-to-Clearinghouse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Security &amp; Identity (CCMS-specific)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Demo PIN seeder script (per-persona known PINs)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — `python -m scripts.seed_demo_pins` from /app/backend sets a known 6-digit PIN on every demo persona (Admin 100001, Doctor 200002, Staff 300003, Patient 400004, Sunrise 600006-900009, Platform 500005). Idempotent; documented in /app/memory/test_credentials.md. PIN is for in-app re-verification, not sign-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Security &amp; Identity (CCMS-specific)</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Login-page demo credentials block (email + password + PIN)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>✅ Shipped</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-04 — /login page renders all four Riverbend demo personas with email, password, and 6-digit PIN visible in plain text. Click a row to auto-fill email + password into the form; PIN is shown beside as text for sensitive-action prompts. Test IDs: login-demo-{role}-email/password/pin.</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3216,7 +3469,7 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
@@ -3226,7 +3479,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
@@ -3236,7 +3489,7 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3246,115 +3499,114 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Features</t>
-        </is>
-      </c>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>By category</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Core Platform &amp; Architecture</t>
+          <t>AI &amp; Automation</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>AI &amp; Automation</t>
+          <t>Billing &amp; RCM</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>EHR &amp; Clinical Documentation</t>
+          <t>Billing &amp; Revenue Cycle</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Patient Intake &amp; Engagement</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Scheduling &amp; Patient Flow</t>
+          <t>Core Platform &amp; Architecture</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Payments &amp; Financial</t>
+          <t>EHR &amp; Clinical Documentation</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Billing &amp; RCM</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Patient Intake &amp; Engagement</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Reporting &amp; Analytics</t>
+          <t>Payments &amp; Financial</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -3364,11 +3616,21 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>Scheduling &amp; Patient Flow</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Security &amp; Identity (CCMS-specific)</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
-        <v>15</v>
+      <c r="B19" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
